--- a/ICHI.xlsx
+++ b/ICHI.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/itech-uw/ConceptMap/ICHI</t>
+    <t>http://fhir.org/guides/who/hiv-dak/ConceptMap/ICHI</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T07:49:07+00:00</t>
+    <t>2024-05-31T12:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/itech-uw/who-smart-hiv-dak/CodeSystem/concept-codes</t>
+    <t>http://fhir.org/guides/who/hiv-dak/CodeSystem/HIV-DAKConcepts</t>
   </si>
   <si>
     <t/>

--- a/ICHI.xlsx
+++ b/ICHI.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T12:57:23+00:00</t>
+    <t>2024-06-06T18:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ICHI.xlsx
+++ b/ICHI.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:19:00+00:00</t>
+    <t>2024-06-06T18:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
